--- a/files/notice/healthcare-agentic-ai-challenge-2026/(양식)2026_Healthcare_AgenticAI_챌린지_신청서.xlsx
+++ b/files/notice/healthcare-agentic-ai-challenge-2026/(양식)2026_Healthcare_AgenticAI_챌린지_신청서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gskku-my.sharepoint.com/personal/ericashin1_g_skku_edu/Documents/AI healthcare lab/agentic ai challege/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/minyoungshin/Documents/aihc_homepage/files/notice/healthcare-agentic-ai-challenge-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4FBB635-9F10-DC42-AB57-D76E29C129EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D28E337E-3FC6-6D47-B7E9-D765EEF42930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{9C38B566-8A65-490F-B157-25B93D40B2E1}"/>
+    <workbookView xWindow="4220" yWindow="7640" windowWidth="30240" windowHeight="18980" xr2:uid="{9C38B566-8A65-490F-B157-25B93D40B2E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,10 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>연구 주제</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>산업공학과</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -85,7 +81,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>사용 데이터셋</t>
+    <t>멀티 에이전트 구성 계획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터셋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -593,16 +593,16 @@
     <col min="5" max="5" width="13.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="13" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="52.5" style="1" customWidth="1"/>
     <col min="11" max="11" width="44.33203125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -644,10 +644,10 @@
         <v>9</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="17">
@@ -661,7 +661,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
